--- a/data/trans_orig/P33B_R3-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P33B_R3-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>25904</t>
+          <t>29326</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11821</t>
+          <t>14227</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50723</t>
+          <t>52163</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13631</t>
+          <t>19150</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5836</t>
+          <t>9045</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27019</t>
+          <t>36955</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>39536</t>
+          <t>48476</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23068</t>
+          <t>29510</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68290</t>
+          <t>74584</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>374083</t>
+          <t>378467</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>349264</t>
+          <t>355630</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>388166</t>
+          <t>393566</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>299569</t>
+          <t>343362</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>286181</t>
+          <t>325557</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>307364</t>
+          <t>353467</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>673651</t>
+          <t>721829</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>644897</t>
+          <t>695721</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>690119</t>
+          <t>740795</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25808</t>
+          <t>26959</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15830</t>
+          <t>15619</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41959</t>
+          <t>43084</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47721</t>
+          <t>52941</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29017</t>
+          <t>39982</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65183</t>
+          <t>67769</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>73529</t>
+          <t>79900</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53346</t>
+          <t>62822</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>95441</t>
+          <t>101927</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>397739</t>
+          <t>449931</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>381588</t>
+          <t>433806</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>407717</t>
+          <t>461271</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>463783</t>
+          <t>448142</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>446321</t>
+          <t>433314</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>482487</t>
+          <t>461101</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>861522</t>
+          <t>898073</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>839610</t>
+          <t>876046</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>881705</t>
+          <t>915151</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>77608</t>
+          <t>83974</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60415</t>
+          <t>67213</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96097</t>
+          <t>104429</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>74842</t>
+          <t>87754</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61816</t>
+          <t>73979</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89707</t>
+          <t>104055</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>152451</t>
+          <t>171727</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>131329</t>
+          <t>150251</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>175080</t>
+          <t>197217</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>457761</t>
+          <t>535875</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>439272</t>
+          <t>515420</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>474954</t>
+          <t>552636</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>467626</t>
+          <t>534385</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>452761</t>
+          <t>518084</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>480652</t>
+          <t>548160</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>925386</t>
+          <t>1070261</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>902757</t>
+          <t>1044771</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>946508</t>
+          <t>1091737</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,9%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>535369</t>
+          <t>619849</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>535369</t>
+          <t>619849</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>535369</t>
+          <t>619849</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1077837</t>
+          <t>1241988</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1077837</t>
+          <t>1241988</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1077837</t>
+          <t>1241988</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>107558</t>
+          <t>117464</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50014</t>
+          <t>98962</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>159441</t>
+          <t>139678</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>153003</t>
+          <t>165057</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>127575</t>
+          <t>144520</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>173330</t>
+          <t>181327</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>260560</t>
+          <t>282522</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>163098</t>
+          <t>256190</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>321693</t>
+          <t>308057</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>780228</t>
+          <t>583153</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>728345</t>
+          <t>560939</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>837772</t>
+          <t>601655</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>559495</t>
+          <t>571438</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>539168</t>
+          <t>555168</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>584923</t>
+          <t>591975</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1339725</t>
+          <t>1154590</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1278592</t>
+          <t>1129055</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1437187</t>
+          <t>1180922</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>82,17%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>98440</t>
+          <t>104447</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83019</t>
+          <t>87011</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>114381</t>
+          <t>122480</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>166306</t>
+          <t>187410</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>148788</t>
+          <t>169685</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>183787</t>
+          <t>205124</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>264746</t>
+          <t>291857</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>242930</t>
+          <t>268667</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>289320</t>
+          <t>319215</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,24%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>461764</t>
+          <t>503818</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>445823</t>
+          <t>485785</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>477185</t>
+          <t>521254</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>379260</t>
+          <t>420723</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>361779</t>
+          <t>403009</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>396778</t>
+          <t>438448</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>841024</t>
+          <t>924540</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>816450</t>
+          <t>897182</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>862840</t>
+          <t>947730</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,91%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1105770</t>
+          <t>1216397</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1105770</t>
+          <t>1216397</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1105770</t>
+          <t>1216397</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>74275</t>
+          <t>83095</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>61658</t>
+          <t>69816</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86642</t>
+          <t>96583</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>124585</t>
+          <t>137771</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55990</t>
+          <t>124107</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>196833</t>
+          <t>152721</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>198861</t>
+          <t>220866</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>106228</t>
+          <t>201512</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>258609</t>
+          <t>241388</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>28,52%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>293890</t>
+          <t>323985</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281523</t>
+          <t>310497</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>306507</t>
+          <t>337264</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>483783</t>
+          <t>301395</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>411535</t>
+          <t>286445</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>552378</t>
+          <t>315059</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>777672</t>
+          <t>625380</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>717924</t>
+          <t>604858</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>870305</t>
+          <t>644734</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>76,19%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>90737</t>
+          <t>100168</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>78373</t>
+          <t>86931</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>103009</t>
+          <t>114320</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>154409</t>
+          <t>172019</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>140294</t>
+          <t>157483</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>168624</t>
+          <t>189203</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>245146</t>
+          <t>272187</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>227985</t>
+          <t>250685</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>265608</t>
+          <t>293538</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,89%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>192022</t>
+          <t>210030</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>179750</t>
+          <t>195878</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>204386</t>
+          <t>223267</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>271422</t>
+          <t>292590</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>257207</t>
+          <t>275406</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>285537</t>
+          <t>307126</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>463444</t>
+          <t>502620</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>442982</t>
+          <t>481269</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>480605</t>
+          <t>524122</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,65%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>500330</t>
+          <t>545433</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>395284</t>
+          <t>502273</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>558367</t>
+          <t>593798</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>734497</t>
+          <t>822101</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>605619</t>
+          <t>778040</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>799633</t>
+          <t>864171</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1234827</t>
+          <t>1367535</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1074122</t>
+          <t>1309728</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1331942</t>
+          <t>1428418</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2957488</t>
+          <t>2985259</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2899451</t>
+          <t>2936894</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3062534</t>
+          <t>3028419</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2924938</t>
+          <t>2912036</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2859802</t>
+          <t>2869966</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3053816</t>
+          <t>2956097</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5882426</t>
+          <t>5897295</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5785311</t>
+          <t>5836412</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6043131</t>
+          <t>5955102</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>81,97%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3457818</t>
+          <t>3530692</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3457818</t>
+          <t>3530692</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3457818</t>
+          <t>3530692</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7117253</t>
+          <t>7264830</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7117253</t>
+          <t>7264830</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7117253</t>
+          <t>7264830</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
